--- a/results/job_matches_2026-05-17.xlsx
+++ b/results/job_matches_2026-05-17.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,25 +503,25 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior DJI Dock 2 / Cloud API Integration Engineer</t>
+          <t>AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Exponent Technology Trading company DWC LLC</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Naperville, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.8</v>
+        <v>18.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Google Cloud Platform, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,19 +531,19 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4968d826aaf9e4d</t>
+          <t>https://www.indeed.com/viewjob?jk=1def15e5de2b7c64</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AWS Cloud Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Educology Solutions</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -556,52 +556,52 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, ECS, IAM, RDS, Scala</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, Scala</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1def15e5de2b7c64</t>
+          <t>https://www.indeed.com/viewjob?jk=ea52f552407f8b0e</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Microsoft Azure Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Educology Solutions</t>
+          <t>CSIK Consulting</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Alexandria, VA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.1</v>
+        <v>16</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea52f552407f8b0e</t>
+          <t>https://www.indeed.com/viewjob?jk=fab3c4481b723cee</t>
         </is>
       </c>
     </row>
@@ -643,17 +643,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Microsoft Azure Engineer</t>
+          <t>Senior Platform, DevOps Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CSIK Consulting</t>
+          <t>CDW</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Alexandria, VA, US USA</t>
+          <t>Vernon Hills, IL, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,59 +661,59 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fab3c4481b723cee</t>
+          <t>https://www.indeed.com/viewjob?jk=10b5742d09907dfe</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Platform, DevOps Engineer</t>
+          <t>Java Full Stack Developer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>CDW</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Vernon Hills, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10b5742d09907dfe</t>
+          <t>https://www.indeed.com/viewjob?jk=966e325f5ac56bee</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Java Full Stack Developer</t>
+          <t>Oracle Cloud Infrastructure (OCI) Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -727,11 +727,11 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Hive, Scala, Oracle, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,14 +741,14 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=966e325f5ac56bee</t>
+          <t>https://www.indeed.com/viewjob?jk=64a90374f14eb8a5</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Oracle Cloud Infrastructure (OCI) Engineer</t>
+          <t>Azure Cloud Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -762,11 +762,11 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Hive, Scala, Oracle, MySQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,137 +776,137 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64a90374f14eb8a5</t>
+          <t>https://www.indeed.com/viewjob?jk=248664e537c28c4d</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sr Advanced Cloud Developer</t>
+          <t>Microsoft Fabric Architect</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Honeywell</t>
+          <t>Troutman Pepper Locke</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Mason, OH, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Event Hubs, GCP, Vertex AI, Spark, Scala, Kafka, ETL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, PySpark, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b77fa4bb580f7b02</t>
+          <t>https://www.indeed.com/viewjob?jk=492db2dfac4c0f4b</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Azure Cloud Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>CDW</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Vernon Hills, IL, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, ETL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=248664e537c28c4d</t>
+          <t>https://www.indeed.com/viewjob?jk=526c7ffc59edd892</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Microsoft Fabric Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Troutman Pepper Locke</t>
+          <t>Fisher Investments</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, PySpark, Scala, SQL Server</t>
+          <t>RDS, Azure, Data Factory, Spark, Scala, Kafka, Oracle, SQL Server, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=492db2dfac4c0f4b</t>
+          <t>https://www.indeed.com/viewjob?jk=1ee849cf602df7fc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Software Engineer, AI Platform</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Fluency</t>
+          <t>Fisher Investments</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Camas, WA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, ECS, RDS, Spark, Dask, Polars</t>
+          <t>RDS, Azure, Data Factory, Spark, Scala, Kafka, Oracle, SQL Server, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,14 +916,14 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9835c2dd64dde09</t>
+          <t>https://www.indeed.com/viewjob?jk=ae7f5047520b4e1a</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -937,11 +937,11 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,172 +951,172 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=526c7ffc59edd892</t>
+          <t>https://www.indeed.com/viewjob?jk=4352558a8280bcbb</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Engineer - Agentic AI</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Troy, MI, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.2</v>
+        <v>11.1</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Docker</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3de44fa63b4b67d2</t>
+          <t>https://www.indeed.com/viewjob?jk=47392e37c7d3ad6b</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Fisher Investments</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, Scala, Kafka, Oracle, SQL Server, NoSQL, ETL</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ee849cf602df7fc</t>
+          <t>https://www.indeed.com/viewjob?jk=8f5c5bf25b4bcc3b</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Fisher Investments</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Camas, WA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, Scala, Kafka, Oracle, SQL Server, NoSQL, ETL</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae7f5047520b4e1a</t>
+          <t>https://www.indeed.com/viewjob?jk=f35198cc5d5a9abe</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Engineer II, Cloud &amp; Web Systems Software</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Masimo</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bf612beac38dd2c</t>
+          <t>https://www.indeed.com/viewjob?jk=6677fe87cb8cb6d6</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Verkada</t>
+          <t>Simplot Company</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ELT, dbt, Airflow, Git</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,67 +1126,67 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d89303a4a06cd252</t>
+          <t>https://www.indeed.com/viewjob?jk=ac7b41fce729d0ab</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>OpenShift Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>CDW</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Vernon Hills, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4352558a8280bcbb</t>
+          <t>https://www.indeed.com/viewjob?jk=080b9674fa248221</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Claims Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Git, Python</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1195,216 +1195,6 @@
         </is>
       </c>
       <c r="G22" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=47392e37c7d3ad6b</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Wells Fargo</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Minneapolis, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>2026-05-16</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8f5c5bf25b4bcc3b</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Wells Fargo</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Columbus, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>2026-05-16</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f35198cc5d5a9abe</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Wells Fargo</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Irving, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>2026-05-16</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6677fe87cb8cb6d6</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Data Engineer III</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Simplot Company</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Boise, ID, US USA</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>2026-05-16</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ac7b41fce729d0ab</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>OpenShift Engineer</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>BV Teck</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>2026-05-16</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=080b9674fa248221</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Claims Data Analytics Engineer</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Bethesda, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Git, Python</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>2026-05-16</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=b781c95a46c79e5d</t>
         </is>

--- a/results/job_matches_2026-05-17.xlsx
+++ b/results/job_matches_2026-05-17.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,60 +538,60 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Microsoft Azure Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Educology Solutions</t>
+          <t>CSIK Consulting</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Alexandria, VA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.1</v>
+        <v>16</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea52f552407f8b0e</t>
+          <t>https://www.indeed.com/viewjob?jk=fab3c4481b723cee</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Microsoft Azure Engineer</t>
+          <t>Java Full Stack Developer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CSIK Consulting</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Alexandria, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fab3c4481b723cee</t>
+          <t>https://www.indeed.com/viewjob?jk=966e325f5ac56bee</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AI Software Engineer III- PySpark, Python, AWS</t>
+          <t>Oracle Cloud Infrastructure (OCI) Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Redshift, S3, RDS, Azure, Databricks, GCP, Spark</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Hive, Scala, Oracle, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,67 +636,67 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=222754f51ea12be7</t>
+          <t>https://www.indeed.com/viewjob?jk=64a90374f14eb8a5</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Platform, DevOps Engineer</t>
+          <t>Azure Cloud Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CDW</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Vernon Hills, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16</v>
+        <v>13.9</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10b5742d09907dfe</t>
+          <t>https://www.indeed.com/viewjob?jk=248664e537c28c4d</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Java Full Stack Developer</t>
+          <t>Microsoft Fabric Architect</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Troutman Pepper Locke</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, PySpark, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,497 +706,217 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=966e325f5ac56bee</t>
+          <t>https://www.indeed.com/viewjob?jk=492db2dfac4c0f4b</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Oracle Cloud Infrastructure (OCI) Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Fisher Investments</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>14.6</v>
+        <v>12.5</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Hive, Scala, Oracle, MySQL, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Spark, Scala, Kafka, Oracle, SQL Server, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64a90374f14eb8a5</t>
+          <t>https://www.indeed.com/viewjob?jk=1ee849cf602df7fc</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Azure Cloud Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Fisher Investments</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Camas, WA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>RDS, Azure, Data Factory, Spark, Scala, Kafka, Oracle, SQL Server, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=248664e537c28c4d</t>
+          <t>https://www.indeed.com/viewjob?jk=ae7f5047520b4e1a</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Microsoft Fabric Architect</t>
+          <t>Data Platform Architect</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Troutman Pepper Locke</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, PySpark, Scala, SQL Server</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=492db2dfac4c0f4b</t>
+          <t>https://www.indeed.com/viewjob?jk=c76fbdb48e9a34d3</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CDW</t>
+          <t>Casey's</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Vernon Hills, IL, US USA</t>
+          <t>Ankeny, IA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, ETL</t>
+          <t>RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=526c7ffc59edd892</t>
+          <t>https://www.indeed.com/viewjob?jk=0d65ad8442e8885d</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Fisher Investments</t>
+          <t>Simplot Company</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, Scala, Kafka, Oracle, SQL Server, NoSQL, ETL</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ee849cf602df7fc</t>
+          <t>https://www.indeed.com/viewjob?jk=ac7b41fce729d0ab</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>OpenShift Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Fisher Investments</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Camas, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, Scala, Kafka, Oracle, SQL Server, NoSQL, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae7f5047520b4e1a</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>CDW</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Vernon Hills, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, ETL</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4352558a8280bcbb</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Wells Fargo</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>2026-05-16</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=47392e37c7d3ad6b</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Wells Fargo</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Minneapolis, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>2026-05-16</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8f5c5bf25b4bcc3b</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Wells Fargo</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Columbus, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>2026-05-16</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f35198cc5d5a9abe</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Wells Fargo</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Irving, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>2026-05-16</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6677fe87cb8cb6d6</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Data Engineer III</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Simplot Company</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Boise, ID, US USA</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>2026-05-16</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ac7b41fce729d0ab</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>OpenShift Engineer</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>BV Teck</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>2026-05-16</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=080b9674fa248221</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Claims Data Analytics Engineer</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Bethesda, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Git, Python</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>2026-05-16</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b781c95a46c79e5d</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-05-17.xlsx
+++ b/results/job_matches_2026-05-17.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -713,17 +713,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Platform Architect</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Fisher Investments</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,190 +731,120 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, Scala, Kafka, Oracle, SQL Server, NoSQL, ETL</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ee849cf602df7fc</t>
+          <t>https://www.indeed.com/viewjob?jk=c76fbdb48e9a34d3</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Fisher Investments</t>
+          <t>Casey's</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Camas, WA, US USA</t>
+          <t>Ankeny, IA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, Scala, Kafka, Oracle, SQL Server, NoSQL, ETL</t>
+          <t>RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae7f5047520b4e1a</t>
+          <t>https://www.indeed.com/viewjob?jk=0d65ad8442e8885d</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Platform Architect</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Simplot Company</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c76fbdb48e9a34d3</t>
+          <t>https://www.indeed.com/viewjob?jk=ac7b41fce729d0ab</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>OpenShift Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Casey's</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ankeny, IA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0d65ad8442e8885d</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Data Engineer III</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Simplot Company</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Boise, ID, US USA</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2026-05-16</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ac7b41fce729d0ab</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>OpenShift Engineer</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>BV Teck</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>2026-05-16</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=080b9674fa248221</t>
         </is>

--- a/results/job_matches_2026-05-17.xlsx
+++ b/results/job_matches_2026-05-17.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,19 +491,19 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cfeff295f2019956</t>
+          <t>https://www.indeed.com/viewjob?jk=4059aa39cd3badff</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AWS Cloud Engineer</t>
+          <t>Hadoop Developer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -517,46 +517,46 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.1</v>
+        <v>20.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, ECS, IAM, RDS, Scala</t>
+          <t>AWS, EMR, RDS, Azure, Databricks, BigQuery, Hadoop, HDFS, Hive, Sqoop</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1def15e5de2b7c64</t>
+          <t>https://www.indeed.com/viewjob?jk=ae893410ec8e0efd</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Microsoft Azure Engineer</t>
+          <t>Hadoop Developer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CSIK Consulting</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Alexandria, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16</v>
+        <v>20.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, EMR, RDS, Azure, Databricks, BigQuery, Hadoop, HDFS, Hive, Sqoop</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,14 +566,14 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fab3c4481b723cee</t>
+          <t>https://www.indeed.com/viewjob?jk=cfeff295f2019956</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Java Full Stack Developer</t>
+          <t>AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -587,28 +587,28 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>15.3</v>
+        <v>18.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=966e325f5ac56bee</t>
+          <t>https://www.indeed.com/viewjob?jk=cefea9656ea9960b</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Oracle Cloud Infrastructure (OCI) Engineer</t>
+          <t>AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -622,28 +622,28 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14.6</v>
+        <v>18.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Hive, Scala, Oracle, MySQL, CI/CD</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64a90374f14eb8a5</t>
+          <t>https://www.indeed.com/viewjob?jk=7748856050bcd694</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Azure Cloud Engineer</t>
+          <t>AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -657,11 +657,11 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13.9</v>
+        <v>18.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=248664e537c28c4d</t>
+          <t>https://www.indeed.com/viewjob?jk=1def15e5de2b7c64</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Microsoft Fabric Architect</t>
+          <t>Microsoft Azure Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Troutman Pepper Locke</t>
+          <t>CSIK Consulting</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Alexandria, VA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13.9</v>
+        <v>16</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, PySpark, Scala, SQL Server</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,14 +706,14 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=492db2dfac4c0f4b</t>
+          <t>https://www.indeed.com/viewjob?jk=fab3c4481b723cee</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Platform Architect</t>
+          <t>Java Full Stack Developer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -727,11 +727,11 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>12.5</v>
+        <v>15.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,67 +741,67 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c76fbdb48e9a34d3</t>
+          <t>https://www.indeed.com/viewjob?jk=cc3a94d9cbf3a341</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Java Full Stack Developer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Casey's</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ankeny, IA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>11.8</v>
+        <v>15.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d65ad8442e8885d</t>
+          <t>https://www.indeed.com/viewjob?jk=6ac195f94bbb2614</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Java Full Stack Developer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Simplot Company</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>10.4</v>
+        <v>15.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,40 +811,705 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac7b41fce729d0ab</t>
+          <t>https://www.indeed.com/viewjob?jk=966e325f5ac56bee</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>Oracle Cloud Infrastructure (OCI) Engineer</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>BV Teck</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, Hive, Scala, Oracle, MySQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=40cd97c169150674</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Oracle Cloud Infrastructure (OCI) Engineer</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>BV Teck</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, Hive, Scala, Oracle, MySQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=276c675b50fafca5</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Oracle Cloud Infrastructure (OCI) Engineer</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>BV Teck</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, Hive, Scala, Oracle, MySQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=64a90374f14eb8a5</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Azure Cloud Engineer</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>BV Teck</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c19dce5d822474c8</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Azure Cloud Engineer</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>BV Teck</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8d93ee6bda9d26db</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Azure Cloud Engineer</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>BV Teck</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=248664e537c28c4d</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Kafka Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>BV Teck</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Event Hubs, Spark, Scala, Spark Streaming, Kafka, Kafka Connect, CI/CD</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e1c513a6cf72498c</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Microsoft Fabric Architect</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Troutman Pepper Locke</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, PySpark, Scala, SQL Server</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=492db2dfac4c0f4b</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Azure Fabric Engineer</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Cyberlocke, LLC</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>McKinney, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Cloud Storage, Spark, PySpark, Scala, ETL, ELT, Power BI</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=75b1d946f299c08c</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Data Platform Architect</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>BV Teck</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=740efe23eed4daac</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Data Platform Architect</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>BV Teck</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c76fbdb48e9a34d3</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Python Developer</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>BV Teck</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>AWS, Glue, S3, RDS, Scala, Oracle, SQL Server, PostgreSQL, DynamoDB, CI/CD</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9a1f0ca7d370b5fc</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Python Developer</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>BV Teck</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>AWS, Glue, S3, RDS, Scala, Oracle, SQL Server, PostgreSQL, DynamoDB, CI/CD</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=36241025a2430295</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Analytics Engineer</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Casey's</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ankeny, IA, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0d65ad8442e8885d</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Mid-Level Azure DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Cyberlocke, LLC</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>McKinney, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Medallion Architecture, ETL, ELT, Power BI, CI/CD, Azure DevOps, Terraform</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ed58b32ec5793dff</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Linux Systems Engineer</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>NTT DATA</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Salt Lake City, UT, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=97dd13894809f36a</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
           <t>OpenShift Engineer</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>BV Teck</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>BV Teck</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
         <v>10.4</v>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ede629cfc3fb969d</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>OpenShift Engineer</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>BV Teck</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=88ad22f9405e77ea</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Data Engineer III</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Simplot Company</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Boise, ID, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
         <is>
           <t>2026-05-16</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ac7b41fce729d0ab</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>OpenShift Engineer</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>BV Teck</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=080b9674fa248221</t>
         </is>

--- a/results/job_matches_2026-05-17.xlsx
+++ b/results/job_matches_2026-05-17.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G31"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,19 +491,19 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4059aa39cd3badff</t>
+          <t>https://www.indeed.com/viewjob?jk=cfeff295f2019956</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hadoop Developer</t>
+          <t>AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -517,46 +517,46 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>20.8</v>
+        <v>18.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, BigQuery, Hadoop, HDFS, Hive, Sqoop</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae893410ec8e0efd</t>
+          <t>https://www.indeed.com/viewjob?jk=1def15e5de2b7c64</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hadoop Developer</t>
+          <t>Microsoft Azure Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>CSIK Consulting</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Alexandria, VA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>20.8</v>
+        <v>16</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, BigQuery, Hadoop, HDFS, Hive, Sqoop</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,14 +566,14 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cfeff295f2019956</t>
+          <t>https://www.indeed.com/viewjob?jk=fab3c4481b723cee</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AWS Cloud Engineer</t>
+          <t>Java Full Stack Developer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -587,28 +587,28 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.1</v>
+        <v>15.3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, ECS, IAM, RDS, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cefea9656ea9960b</t>
+          <t>https://www.indeed.com/viewjob?jk=966e325f5ac56bee</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AWS Cloud Engineer</t>
+          <t>Oracle Cloud Infrastructure (OCI) Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -622,28 +622,28 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>18.1</v>
+        <v>14.6</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, ECS, IAM, RDS, Scala</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Hive, Scala, Oracle, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7748856050bcd694</t>
+          <t>https://www.indeed.com/viewjob?jk=64a90374f14eb8a5</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AWS Cloud Engineer</t>
+          <t>Azure Cloud Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -657,11 +657,11 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>18.1</v>
+        <v>13.9</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, ECS, IAM, RDS, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1def15e5de2b7c64</t>
+          <t>https://www.indeed.com/viewjob?jk=248664e537c28c4d</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Microsoft Azure Engineer</t>
+          <t>Azure Fabric Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>CSIK Consulting</t>
+          <t>Cyberlocke, LLC</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Alexandria, VA, US USA</t>
+          <t>McKinney, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16</v>
+        <v>13.2</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>RDS, Azure, Data Factory, Cloud Storage, Spark, PySpark, Scala, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,14 +706,14 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fab3c4481b723cee</t>
+          <t>https://www.indeed.com/viewjob?jk=75b1d946f299c08c</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Java Full Stack Developer</t>
+          <t>Data Platform Architect</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -727,11 +727,11 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>15.3</v>
+        <v>12.5</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,67 +741,67 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc3a94d9cbf3a341</t>
+          <t>https://www.indeed.com/viewjob?jk=c76fbdb48e9a34d3</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Java Full Stack Developer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Casey's</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Ankeny, IA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>15.3</v>
+        <v>11.8</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ac195f94bbb2614</t>
+          <t>https://www.indeed.com/viewjob?jk=0d65ad8442e8885d</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Java Full Stack Developer</t>
+          <t>Mid-Level Azure DevOps Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Cyberlocke, LLC</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>McKinney, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>15.3</v>
+        <v>11.1</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>RDS, Azure, Data Factory, Medallion Architecture, ETL, ELT, Power BI, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=966e325f5ac56bee</t>
+          <t>https://www.indeed.com/viewjob?jk=ed58b32ec5793dff</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Oracle Cloud Infrastructure (OCI) Engineer</t>
+          <t>Linux Systems Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>14.6</v>
+        <v>11.1</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Hive, Scala, Oracle, MySQL, CI/CD</t>
+          <t>AWS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,49 +846,49 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40cd97c169150674</t>
+          <t>https://www.indeed.com/viewjob?jk=97dd13894809f36a</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Oracle Cloud Infrastructure (OCI) Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Simplot Company</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>14.6</v>
+        <v>10.4</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Hive, Scala, Oracle, MySQL, CI/CD</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=276c675b50fafca5</t>
+          <t>https://www.indeed.com/viewjob?jk=ac7b41fce729d0ab</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Oracle Cloud Infrastructure (OCI) Engineer</t>
+          <t>OpenShift Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -902,11 +902,11 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>14.6</v>
+        <v>10.4</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Hive, Scala, Oracle, MySQL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -915,601 +915,6 @@
         </is>
       </c>
       <c r="G14" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=64a90374f14eb8a5</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Azure Cloud Engineer</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>BV Teck</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c19dce5d822474c8</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Azure Cloud Engineer</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>BV Teck</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8d93ee6bda9d26db</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Azure Cloud Engineer</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>BV Teck</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>2026-05-16</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=248664e537c28c4d</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Kafka Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>BV Teck</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Event Hubs, Spark, Scala, Spark Streaming, Kafka, Kafka Connect, CI/CD</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e1c513a6cf72498c</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Microsoft Fabric Architect</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Troutman Pepper Locke</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, PySpark, Scala, SQL Server</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>2026-05-16</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=492db2dfac4c0f4b</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Azure Fabric Engineer</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Cyberlocke, LLC</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>McKinney, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Cloud Storage, Spark, PySpark, Scala, ETL, ELT, Power BI</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>2026-05-16</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=75b1d946f299c08c</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Data Platform Architect</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>BV Teck</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=740efe23eed4daac</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Data Platform Architect</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>BV Teck</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c76fbdb48e9a34d3</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Python Developer</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>BV Teck</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>AWS, Glue, S3, RDS, Scala, Oracle, SQL Server, PostgreSQL, DynamoDB, CI/CD</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9a1f0ca7d370b5fc</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Python Developer</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>BV Teck</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>AWS, Glue, S3, RDS, Scala, Oracle, SQL Server, PostgreSQL, DynamoDB, CI/CD</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=36241025a2430295</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Analytics Engineer</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Casey's</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ankeny, IA, US USA</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0d65ad8442e8885d</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Mid-Level Azure DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Cyberlocke, LLC</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>McKinney, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Medallion Architecture, ETL, ELT, Power BI, CI/CD, Azure DevOps, Terraform</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>2026-05-16</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ed58b32ec5793dff</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Linux Systems Engineer</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>NTT DATA</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Salt Lake City, UT, US USA</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=97dd13894809f36a</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>OpenShift Engineer</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>BV Teck</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ede629cfc3fb969d</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>OpenShift Engineer</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>BV Teck</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=88ad22f9405e77ea</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Data Engineer III</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Simplot Company</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Boise, ID, US USA</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>2026-05-16</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ac7b41fce729d0ab</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>OpenShift Engineer</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>BV Teck</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>2026-05-16</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=080b9674fa248221</t>
         </is>

--- a/results/job_matches_2026-05-17.xlsx
+++ b/results/job_matches_2026-05-17.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -818,52 +818,52 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Linux Systems Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Simplot Company</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97dd13894809f36a</t>
+          <t>https://www.indeed.com/viewjob?jk=ac7b41fce729d0ab</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>OpenShift Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Simplot Company</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -880,41 +880,6 @@
         </is>
       </c>
       <c r="G13" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ac7b41fce729d0ab</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>OpenShift Engineer</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>BV Teck</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>2026-05-16</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=080b9674fa248221</t>
         </is>

--- a/results/job_matches_2026-05-17.xlsx
+++ b/results/job_matches_2026-05-17.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,25 +538,25 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Microsoft Azure Engineer</t>
+          <t>Java Full Stack Developer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CSIK Consulting</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Alexandria, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,14 +566,14 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fab3c4481b723cee</t>
+          <t>https://www.indeed.com/viewjob?jk=966e325f5ac56bee</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Java Full Stack Developer</t>
+          <t>Oracle Cloud Infrastructure (OCI) Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -587,11 +587,11 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Hive, Scala, Oracle, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,14 +601,14 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=966e325f5ac56bee</t>
+          <t>https://www.indeed.com/viewjob?jk=64a90374f14eb8a5</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Oracle Cloud Infrastructure (OCI) Engineer</t>
+          <t>Azure Cloud Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -622,11 +622,11 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Hive, Scala, Oracle, MySQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64a90374f14eb8a5</t>
+          <t>https://www.indeed.com/viewjob?jk=248664e537c28c4d</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Azure Cloud Engineer</t>
+          <t>Azure Fabric Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Cyberlocke, LLC</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>McKinney, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>RDS, Azure, Data Factory, Cloud Storage, Spark, PySpark, Scala, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,137 +671,137 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=248664e537c28c4d</t>
+          <t>https://www.indeed.com/viewjob?jk=75b1d946f299c08c</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Azure Fabric Engineer</t>
+          <t>Data Platform Architect</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Cyberlocke, LLC</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>McKinney, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Cloud Storage, Spark, PySpark, Scala, ETL, ELT, Power BI</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75b1d946f299c08c</t>
+          <t>https://www.indeed.com/viewjob?jk=c76fbdb48e9a34d3</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Platform Architect</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Casey's</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Ankeny, IA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
+          <t>RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c76fbdb48e9a34d3</t>
+          <t>https://www.indeed.com/viewjob?jk=0d65ad8442e8885d</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Mid-Level Azure DevOps Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Casey's</t>
+          <t>Cyberlocke, LLC</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ankeny, IA, US USA</t>
+          <t>McKinney, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI</t>
+          <t>RDS, Azure, Data Factory, Medallion Architecture, ETL, ELT, Power BI, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d65ad8442e8885d</t>
+          <t>https://www.indeed.com/viewjob?jk=ed58b32ec5793dff</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Mid-Level Azure DevOps Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Cyberlocke, LLC</t>
+          <t>Simplot Company</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>McKinney, TX, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Medallion Architecture, ETL, ELT, Power BI, CI/CD, Azure DevOps, Terraform</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed58b32ec5793dff</t>
+          <t>https://www.indeed.com/viewjob?jk=ac7b41fce729d0ab</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>OpenShift Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Simplot Company</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -845,41 +845,6 @@
         </is>
       </c>
       <c r="G12" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ac7b41fce729d0ab</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>OpenShift Engineer</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>BV Teck</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2026-05-16</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=080b9674fa248221</t>
         </is>

--- a/results/job_matches_2026-05-17.xlsx
+++ b/results/job_matches_2026-05-17.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Hadoop Developer</t>
+          <t>Azure Fabric Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Cyberlocke, LLC</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>McKinney, TX, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>20.8</v>
+        <v>13.2</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, BigQuery, Hadoop, HDFS, Hive, Sqoop</t>
+          <t>RDS, Azure, Data Factory, Cloud Storage, Spark, PySpark, Scala, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,14 +496,14 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cfeff295f2019956</t>
+          <t>https://www.indeed.com/viewjob?jk=75b1d946f299c08c</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AWS Cloud Engineer</t>
+          <t>Data Platform Architect</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -517,116 +517,116 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.1</v>
+        <v>12.5</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, ECS, IAM, RDS, Scala</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1def15e5de2b7c64</t>
+          <t>https://www.indeed.com/viewjob?jk=c76fbdb48e9a34d3</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Java Full Stack Developer</t>
+          <t>Cloud Engineer Specialist</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Technology Ventures</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15.3</v>
+        <v>11.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, S3, API Gateway, ECS, IAM, RDS, Azure, GCP, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=966e325f5ac56bee</t>
+          <t>https://www.indeed.com/viewjob?jk=97c3d08d72035c3d</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Oracle Cloud Infrastructure (OCI) Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Casey's</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Ankeny, IA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14.6</v>
+        <v>11.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Hive, Scala, Oracle, MySQL, CI/CD</t>
+          <t>RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64a90374f14eb8a5</t>
+          <t>https://www.indeed.com/viewjob?jk=0d65ad8442e8885d</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Azure Cloud Engineer</t>
+          <t>Mid-Level Azure DevOps Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Cyberlocke, LLC</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>McKinney, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13.9</v>
+        <v>11.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>RDS, Azure, Data Factory, Medallion Architecture, ETL, ELT, Power BI, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=248664e537c28c4d</t>
+          <t>https://www.indeed.com/viewjob?jk=ed58b32ec5793dff</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Azure Fabric Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Cyberlocke, LLC</t>
+          <t>Simplot Company</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>McKinney, TX, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13.2</v>
+        <v>10.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Cloud Storage, Spark, PySpark, Scala, ETL, ELT, Power BI</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,182 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75b1d946f299c08c</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Data Platform Architect</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>BV Teck</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c76fbdb48e9a34d3</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Analytics Engineer</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Casey's</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ankeny, IA, US USA</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0d65ad8442e8885d</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Mid-Level Azure DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Cyberlocke, LLC</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>McKinney, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Medallion Architecture, ETL, ELT, Power BI, CI/CD, Azure DevOps, Terraform</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>2026-05-16</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ed58b32ec5793dff</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Data Engineer III</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Simplot Company</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Boise, ID, US USA</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>2026-05-16</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=ac7b41fce729d0ab</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>OpenShift Engineer</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>BV Teck</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2026-05-16</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=080b9674fa248221</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-05-17.xlsx
+++ b/results/job_matches_2026-05-17.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,42 +468,42 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Azure Fabric Engineer</t>
+          <t>Hadoop Developer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Cyberlocke, LLC</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>McKinney, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>13.2</v>
+        <v>20.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Cloud Storage, Spark, PySpark, Scala, ETL, ELT, Power BI</t>
+          <t>AWS, EMR, RDS, Azure, Databricks, BigQuery, Hadoop, HDFS, Hive, Sqoop</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75b1d946f299c08c</t>
+          <t>https://www.indeed.com/viewjob?jk=8373a741b052d44b</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Platform Architect</t>
+          <t>AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -517,11 +517,11 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>12.5</v>
+        <v>18.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c76fbdb48e9a34d3</t>
+          <t>https://www.indeed.com/viewjob?jk=30f833e04719a9a2</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Cloud Engineer Specialist</t>
+          <t>Java Full Stack Developer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Technology Ventures</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>11.8</v>
+        <v>15.3</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, ECS, IAM, RDS, Azure, GCP, Jenkins, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,110 +566,460 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97c3d08d72035c3d</t>
+          <t>https://www.indeed.com/viewjob?jk=cddc6dae0826bd04</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Oracle Cloud Infrastructure (OCI) Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Casey's</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ankeny, IA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>11.8</v>
+        <v>14.6</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Hive, Scala, Oracle, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d65ad8442e8885d</t>
+          <t>https://www.indeed.com/viewjob?jk=ffa69b7b9b8f26ea</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Mid-Level Azure DevOps Engineer</t>
+          <t>Azure Cloud Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Cyberlocke, LLC</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>McKinney, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11.1</v>
+        <v>13.9</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Medallion Architecture, ETL, ELT, Power BI, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed58b32ec5793dff</t>
+          <t>https://www.indeed.com/viewjob?jk=956c92978bddfb05</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>Kafka Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>BV Teck</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Event Hubs, Spark, Scala, Spark Streaming, Kafka, Kafka Connect, CI/CD</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7e94fc972b257aa1</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Kafka Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>BV Teck</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Event Hubs, Spark, Scala, Spark Streaming, Kafka, Kafka Connect, CI/CD</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3244d4338143c6aa</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Azure Fabric Engineer</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Cyberlocke, LLC</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>McKinney, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Cloud Storage, Spark, PySpark, Scala, ETL, ELT, Power BI</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=75b1d946f299c08c</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Data Platform Architect</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>BV Teck</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=136b290a5c76ca43</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Data Platform Architect</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>BV Teck</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c76fbdb48e9a34d3</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Cloud Engineer Specialist</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Technology Ventures</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>AWS, S3, API Gateway, ECS, IAM, RDS, Azure, GCP, Jenkins, Terraform</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=97c3d08d72035c3d</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Python Developer</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>BV Teck</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>AWS, Glue, S3, RDS, Scala, Oracle, SQL Server, PostgreSQL, DynamoDB, CI/CD</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=649989a8ef5488a3</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Analytics Engineer</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Casey's</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ankeny, IA, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0d65ad8442e8885d</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Mid-Level Azure DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Cyberlocke, LLC</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>McKinney, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Medallion Architecture, ETL, ELT, Power BI, CI/CD, Azure DevOps, Terraform</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ed58b32ec5793dff</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>OpenShift Engineer</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>BV Teck</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3b64925ef829beee</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>Data Engineer III</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>Simplot Company</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>Boise, ID, US USA</t>
         </is>
       </c>
-      <c r="D7" t="n">
+      <c r="D17" t="n">
         <v>10.4</v>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>2026-05-16</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=ac7b41fce729d0ab</t>
         </is>

--- a/results/job_matches_2026-05-17.xlsx
+++ b/results/job_matches_2026-05-17.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,42 +468,42 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Hadoop Developer</t>
+          <t>Azure Fabric Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Cyberlocke, LLC</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>McKinney, TX, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>20.8</v>
+        <v>13.2</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, BigQuery, Hadoop, HDFS, Hive, Sqoop</t>
+          <t>RDS, Azure, Data Factory, Cloud Storage, Spark, PySpark, Scala, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8373a741b052d44b</t>
+          <t>https://www.indeed.com/viewjob?jk=75b1d946f299c08c</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AWS Cloud Engineer</t>
+          <t>Data Platform Architect</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -517,11 +517,11 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.1</v>
+        <v>12.5</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, ECS, IAM, RDS, Scala</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30f833e04719a9a2</t>
+          <t>https://www.indeed.com/viewjob?jk=c76fbdb48e9a34d3</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Java Full Stack Developer</t>
+          <t>Cloud Engineer Specialist</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Technology Ventures</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15.3</v>
+        <v>11.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, S3, API Gateway, ECS, IAM, RDS, Azure, GCP, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,462 +566,77 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cddc6dae0826bd04</t>
+          <t>https://www.indeed.com/viewjob?jk=97c3d08d72035c3d</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Oracle Cloud Infrastructure (OCI) Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Casey's</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Ankeny, IA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14.6</v>
+        <v>11.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Hive, Scala, Oracle, MySQL, CI/CD</t>
+          <t>RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffa69b7b9b8f26ea</t>
+          <t>https://www.indeed.com/viewjob?jk=0d65ad8442e8885d</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Azure Cloud Engineer</t>
+          <t>Mid-Level Azure DevOps Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Cyberlocke, LLC</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>McKinney, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13.9</v>
+        <v>11.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>RDS, Azure, Data Factory, Medallion Architecture, ETL, ELT, Power BI, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=956c92978bddfb05</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Kafka Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>BV Teck</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Event Hubs, Spark, Scala, Spark Streaming, Kafka, Kafka Connect, CI/CD</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7e94fc972b257aa1</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Kafka Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>BV Teck</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Event Hubs, Spark, Scala, Spark Streaming, Kafka, Kafka Connect, CI/CD</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3244d4338143c6aa</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Azure Fabric Engineer</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Cyberlocke, LLC</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>McKinney, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Cloud Storage, Spark, PySpark, Scala, ETL, ELT, Power BI</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>2026-05-16</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=75b1d946f299c08c</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Data Platform Architect</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>BV Teck</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=136b290a5c76ca43</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Data Platform Architect</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>BV Teck</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c76fbdb48e9a34d3</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Cloud Engineer Specialist</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Technology Ventures</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>McLean, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>AWS, S3, API Gateway, ECS, IAM, RDS, Azure, GCP, Jenkins, Terraform</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=97c3d08d72035c3d</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Python Developer</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>BV Teck</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>AWS, Glue, S3, RDS, Scala, Oracle, SQL Server, PostgreSQL, DynamoDB, CI/CD</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=649989a8ef5488a3</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Analytics Engineer</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Casey's</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ankeny, IA, US USA</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0d65ad8442e8885d</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Mid-Level Azure DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Cyberlocke, LLC</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>McKinney, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Medallion Architecture, ETL, ELT, Power BI, CI/CD, Azure DevOps, Terraform</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2026-05-16</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=ed58b32ec5793dff</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>OpenShift Engineer</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>BV Teck</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3b64925ef829beee</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Data Engineer III</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Simplot Company</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Boise, ID, US USA</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>2026-05-16</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ac7b41fce729d0ab</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-05-17.xlsx
+++ b/results/job_matches_2026-05-17.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -637,6 +637,76 @@
       <c r="G6" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=ed58b32ec5793dff</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Linux Systems Engineer</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>NTT DATA</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Salt Lake City, UT, US USA</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=97dd13894809f36a</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Data Architect</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Cisco</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, Git</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=49bdfaf2b8654cd8</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-05-17.xlsx
+++ b/results/job_matches_2026-05-17.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -637,76 +637,6 @@
       <c r="G6" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=ed58b32ec5793dff</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Linux Systems Engineer</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>NTT DATA</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Salt Lake City, UT, US USA</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=97dd13894809f36a</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Data Architect</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Cisco</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>San Jose, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, Git</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=49bdfaf2b8654cd8</t>
         </is>
       </c>
     </row>
